--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_magallanes_y_la_antartica_chilena.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>25.65913009103188</v>
+      </c>
+      <c r="C2">
         <v>32.53868031229754</v>
-      </c>
-      <c r="C2">
-        <v>25.65913009103188</v>
       </c>
       <c r="D2">
         <v>3.073265388768899</v>
       </c>
       <c r="E2">
-        <v>20.56835061707828</v>
+        <v>16.21964932739161</v>
       </c>
       <c r="F2">
         <v>63.2120000555301</v>
       </c>
       <c r="G2">
-        <v>16.21964932739161</v>
+        <v>20.56835061707828</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>25.37313432835821</v>
+      </c>
+      <c r="C3">
         <v>40.29850746268657</v>
-      </c>
-      <c r="C3">
-        <v>25.37313432835821</v>
       </c>
       <c r="D3">
         <v>2.481481481481481</v>
       </c>
       <c r="E3">
-        <v>24.32432432432432</v>
+        <v>15.31531531531532</v>
       </c>
       <c r="F3">
         <v>60.36036036036036</v>
       </c>
       <c r="G3">
-        <v>15.31531531531532</v>
+        <v>24.32432432432432</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>14.01869158878505</v>
+      </c>
+      <c r="C4">
         <v>28.97196261682243</v>
-      </c>
-      <c r="C4">
-        <v>14.01869158878505</v>
       </c>
       <c r="D4">
         <v>3.451612903225806</v>
       </c>
       <c r="E4">
-        <v>20.26143790849673</v>
+        <v>9.80392156862745</v>
       </c>
       <c r="F4">
         <v>69.93464052287581</v>
       </c>
       <c r="G4">
-        <v>9.80392156862745</v>
+        <v>20.26143790849673</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>32.25806451612903</v>
+      </c>
+      <c r="C5">
         <v>34.83870967741935</v>
-      </c>
-      <c r="C5">
-        <v>32.25806451612903</v>
       </c>
       <c r="D5">
         <v>2.87037037037037</v>
       </c>
       <c r="E5">
-        <v>20.84942084942085</v>
+        <v>19.30501930501931</v>
       </c>
       <c r="F5">
         <v>59.84555984555985</v>
       </c>
       <c r="G5">
-        <v>19.30501930501931</v>
+        <v>20.84942084942085</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>35.39823008849557</v>
+      </c>
+      <c r="C6">
         <v>13.49557522123894</v>
-      </c>
-      <c r="C6">
-        <v>35.39823008849557</v>
       </c>
       <c r="D6">
         <v>7.409836065573771</v>
       </c>
       <c r="E6">
-        <v>9.063893016344725</v>
+        <v>23.7741456166419</v>
       </c>
       <c r="F6">
         <v>67.16196136701338</v>
       </c>
       <c r="G6">
-        <v>23.7741456166419</v>
+        <v>9.063893016344725</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.15320392402421</v>
+      </c>
+      <c r="C7">
         <v>26.3828010853684</v>
-      </c>
-      <c r="C7">
-        <v>26.15320392402421</v>
       </c>
       <c r="D7">
         <v>3.790348101265823</v>
       </c>
       <c r="E7">
-        <v>17.29611384783799</v>
+        <v>17.1455938697318</v>
       </c>
       <c r="F7">
         <v>65.5582922824302</v>
       </c>
       <c r="G7">
-        <v>17.1455938697318</v>
+        <v>17.29611384783799</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>36.15819209039548</v>
+      </c>
+      <c r="C8">
         <v>31.35593220338983</v>
-      </c>
-      <c r="C8">
-        <v>36.15819209039548</v>
       </c>
       <c r="D8">
         <v>3.189189189189189</v>
       </c>
       <c r="E8">
-        <v>18.71838111298482</v>
+        <v>21.58516020236087</v>
       </c>
       <c r="F8">
         <v>59.6964586846543</v>
       </c>
       <c r="G8">
-        <v>21.58516020236087</v>
+        <v>18.71838111298482</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.53012048192771</v>
+      </c>
+      <c r="C9">
         <v>28.91566265060241</v>
-      </c>
-      <c r="C9">
-        <v>32.53012048192771</v>
       </c>
       <c r="D9">
         <v>3.458333333333333</v>
       </c>
       <c r="E9">
-        <v>17.91044776119404</v>
+        <v>20.14925373134328</v>
       </c>
       <c r="F9">
         <v>61.94029850746269</v>
       </c>
       <c r="G9">
-        <v>20.14925373134329</v>
+        <v>17.91044776119403</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>24.75043402777778</v>
+      </c>
+      <c r="C10">
         <v>29.88823784722222</v>
-      </c>
-      <c r="C10">
-        <v>24.75043402777778</v>
       </c>
       <c r="D10">
         <v>3.345797785442004</v>
       </c>
       <c r="E10">
-        <v>19.32779005718696</v>
+        <v>16.00533277198891</v>
       </c>
       <c r="F10">
         <v>64.66687717082412</v>
       </c>
       <c r="G10">
-        <v>16.00533277198891</v>
+        <v>19.32779005718696</v>
       </c>
     </row>
     <row r="11">
